--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2501_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2501_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,14 +666,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FS2501-08-06-FG</t>
+          <t>FS2501-08-08-FG</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="D2" t="n">
         <v>0.40625</v>
@@ -697,22 +697,22 @@
         <v>0.2125</v>
       </c>
       <c r="K2" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="L2" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="M2" t="n">
-        <v>0.32823</v>
+        <v>0.40779</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4078</v>
+        <v>0.5337</v>
       </c>
       <c r="O2" t="n">
         <v>1.7899</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1522</v>
+        <v>0.2163</v>
       </c>
       <c r="Q2" t="n">
         <v>0.37</v>
@@ -721,10 +721,10 @@
         <v>1.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="T2" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="U2" t="n">
         <v>0.8125</v>
@@ -745,93 +745,1469 @@
         <v>0.0625</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.65645</v>
+        <v>0.81557</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4078</v>
+        <v>0.5337</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05556</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.32823</v>
+        <v>0.40779</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.28378</v>
+        <v>0.35064</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="AH2" t="n">
         <v>0.596</v>
       </c>
       <c r="AI2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>FS2501-08-08-FG</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 13/16-16 UN (male O-ring face seal, SAE J1453) x 1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>FS2501</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "M LGTH" = "1.10" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 118.0, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; N@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "N LGTH" = "1.47" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 118.0, page verified True) [Brennan = yes 2026-10-18] - pipe leg tip -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "JJ FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 118.0, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -08 = 0.8125 (PLAN.md s2 FS_THR / the -08 thread of every staged ORFS row); = Brennan "A THREAD" "13/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "A THREAD" "13/16-16" in the table's format; $PRP@Thread_A: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "B THREAD" "1/2-14" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "TUBE O.D." "1/2" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2501: FSM -08 bore on 2 Air-Way row(s): 0.37 (unanimous) [Air-Way, not Brennan]; D2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2501: NPTF -08 bore on 1 Air-Way row(s): 0.53 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on JJ FLATS=0.875 vs Air-Way S2=0.94 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5369 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p8 FS2501-08-08-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>FS2501-08-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FS2501-06-04-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="F3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.75</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AH3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>FS2501-06-04-FG</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 11/16-16 UN (male O-ring face seal, SAE J1453) x 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>FS2501</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Air-Way FF2501 (s21, double-pass 2026-10-15, parts.air-way.com/api/series/21, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2501-06-04-FG (ORFS-p008-t01); FORGED part: Air-Way NON-forged row FF2501-6-4-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2501-6-4-O = Brennan forged FS2501-06-04-FG p8 on every compared cell (M LGTH ~ L7, N LGTH ~ N, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5365 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>FS2501-06-04-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FS2501-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>0.66</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AK4" t="n">
         <v>0.375</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AL4" t="n">
         <v>0.375</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AM4" t="n">
         <v>0.21601</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN4" t="n">
         <v>0.21601</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AO4" t="n">
         <v>0.43251</v>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>FS2501-06-06-FG</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 11/16-16 UN (male O-ring face seal, SAE J1453) x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>FS2501</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-06-06-FG col "M LGTH" = "0.980" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 77.6, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; N@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-06-06-FG col "N LGTH" = "1.220" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 77.6, page verified True) [Brennan = yes 2026-10-18] - pipe leg tip -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-06-06-FG col "JJ FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 77.6, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "A THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-06-06-FG col "A THREAD" "11/16-16" in the table's format; $PRP@Thread_A: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-06-06-FG col "B THREAD" "3/8-18" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-06-06-FG col "TUBE O.D." "3/8" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2501: FSM -06 bore on 2 Air-Way row(s): 0.26 (unanimous) [Air-Way, not Brennan]; D2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2501: NPTF -06 bore on 2 Air-Way row(s): 0.41 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on M LGTH=0.980 vs Air-Way L7=1.04 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5366 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p8 FS2501-06-06-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>FS2501-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FS2501-06-08-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.50757</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>FS2501-06-08-FG</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 11/16-16 UN (male O-ring face seal, SAE J1453) x 1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>FS2501</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>Air-Way FF2501 (s21, double-pass 2026-10-15, parts.air-way.com/api/series/21, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2501-06-08-FG (ORFS-p008-t01); FORGED part: Air-Way NON-forged row FF2501-6-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2501-6-8-O = Brennan forged FS2501-06-08-FG p8 on every compared cell (M LGTH ~ L7, N LGTH ~ N, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5367 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>FS2501-06-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>FS2501-08-06-FG</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="B6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>FS2501-08-06-FG</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 13/16-16 UN (male O-ring face seal, SAE J1453) x 3/8-18 NPTF</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>FS2501</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>3/8-18 NPTF</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>Air-Way FF2501 (s21, double-pass 2026-10-15, parts.air-way.com/api/series/21, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2501-08-06-FG (ORFS-p008-t01); FORGED part: Air-Way NON-forged row FF2501-8-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length = gen_straight2 FSM_MEAS (Brennan FS2403-08-08); on the forged legs the thread major runs to the end length and steps down to the hex flats (Brennan FS6500 / FS6801 / FS2701-08 forged legs) - the end stands proud of the flats; hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>Air-Way FF2501 (s21, double-pass 2026-10-15, parts.air-way.com/api/series/21, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2501-08-06-FG (ORFS-p008-t01); FORGED part: Air-Way NON-forged row FF2501-8-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
         <is>
           <t>forged (-FG): Air-Way non-forged FF2501-8-6-O = Brennan forged FS2501-08-06-FG p8 on every compared cell (M LGTH ~ L7, N LGTH ~ N, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5368 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>FS2501-08-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FS2501-08-12-FG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="F7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.61149</v>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>FS2501-08-12-FG</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 13/16-16 UN (male O-ring face seal, SAE J1453) x 3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>FS2501</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>Air-Way FF2501 (s21, double-pass 2026-10-15, parts.air-way.com/api/series/21, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2501-08-12-FG (ORFS-p008-t01); FORGED part: Air-Way NON-forged row FF2501-8-12-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2501-8-12-O = Brennan forged FS2501-08-12-FG p8 on every compared cell (M LGTH ~ L7, N LGTH ~ N, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | Air-Way thread printing slip: d UN/UNF-2A "3/16-16" where Air-Way prints 13/16-16 for this dash - THDMAJ left empty, the thread comes from the end library by dash (plan D1) | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5370 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs) | THDMAJ_D@DRIVE empty: thread major 0.8125 = the -08 end library (Q-TRANSFER-ENDLIB); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>FS2501-08-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FS2501-10-08-FG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="F8" t="n">
+        <v>45</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.61265</v>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>FS2501-10-08-FG</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 1-14 UN (male O-ring face seal, SAE J1453) x 1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>FS2501</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-10-08-FG col "M LGTH" = "1.310" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 148.2, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; N@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-10-08-FG col "N LGTH" = "1.470" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 148.2, page verified True) [Brennan = yes 2026-10-18] - pipe leg tip -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-10-08-FG col "JJ FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 148.2, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -10 = 1.0 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "A THREAD" "1-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-10-08-FG col "A THREAD" "1-14" in the table's format; $PRP@Thread_A: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-10-08-FG col "B THREAD" "1/2-14" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-10-08-FG col "TUBE O.D." "5/8" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2501: FSM -10 bore on 1 Air-Way row(s): 0.49 (unanimous) [Air-Way, not Brennan]; D2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2501: NPTF -08 bore on 1 Air-Way row(s): 0.53 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on JJ FLATS=1.062 vs Air-Way S2=0.94 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5371 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p8 FS2501-10-08-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>FS2501-10-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FS2501-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="F9" t="n">
+        <v>45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.68077</v>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>FS2501-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 1 3/16-12 UN (male O-ring face seal, SAE J1453) x 3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>FS2501</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1 3/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>Air-Way FF2501 (s21, double-pass 2026-10-15, parts.air-way.com/api/series/21, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2501-12-12-FG (ORFS-p008-t01); FORGED part: Air-Way NON-forged row FF2501-12-12-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2501-12-12-O = Brennan forged FS2501-12-12-FG p8 on every compared cell (M LGTH ~ L7, N LGTH ~ N, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5373 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>FS2501-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FS2501-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="F10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.94058</v>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>FS2501-20-20-FG</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 1 11/16-12 UN (male O-ring face seal, SAE J1453) x 1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>FS2501</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>Air-Way FF2501 (s21, double-pass 2026-10-15, parts.air-way.com/api/series/21, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2501-20-20-FG (ORFS-p008-t01); FORGED part: Air-Way NON-forged row FF2501-20-20-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2501-20-20-O = Brennan forged FS2501-20-20-FG p8 on every compared cell (M LGTH ~ L7, N LGTH ~ N, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5375 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs) | leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>FS2501-20-20-FG</t>
         </is>
       </c>
     </row>

--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2501_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2501_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -666,14 +666,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FS2501-08-08-FG</t>
+          <t>FS2501-08-06-FG</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="D2" t="n">
         <v>0.40625</v>
@@ -697,22 +697,22 @@
         <v>0.2125</v>
       </c>
       <c r="K2" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="M2" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="O2" t="n">
         <v>1.7899</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2163</v>
+        <v>0.1522</v>
       </c>
       <c r="Q2" t="n">
         <v>0.37</v>
@@ -721,10 +721,10 @@
         <v>1.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="T2" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="U2" t="n">
         <v>0.8125</v>
@@ -745,58 +745,58 @@
         <v>0.0625</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.81557</v>
+        <v>0.65645</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.35064</v>
+        <v>0.28378</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AH2" t="n">
         <v>0.596</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.25209</v>
+        <v>0.21601</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.25209</v>
+        <v>0.21601</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.50468</v>
+        <v>0.43251</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>FS2501-08-08-FG</t>
+          <t>FS2501-08-06-FG</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 13/16-16 UN (male O-ring face seal, SAE J1453) x 1/2-14 NPTF</t>
+          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 13/16-16 UN (male O-ring face seal, SAE J1453) x 3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "M LGTH" = "1.10" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 118.0, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; N@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "N LGTH" = "1.47" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 118.0, page verified True) [Brennan = yes 2026-10-18] - pipe leg tip -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "JJ FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 118.0, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -08 = 0.8125 (PLAN.md s2 FS_THR / the -08 thread of every staged ORFS row); = Brennan "A THREAD" "13/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "A THREAD" "13/16-16" in the table's format; $PRP@Thread_A: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "B THREAD" "1/2-14" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "TUBE O.D." "1/2" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2501: FSM -08 bore on 2 Air-Way row(s): 0.37 (unanimous) [Air-Way, not Brennan]; D2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2501: NPTF -08 bore on 1 Air-Way row(s): 0.53 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF2501 (s21, double-pass 2026-10-15, parts.air-way.com/api/series/21, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2501-08-06-FG (ORFS-p008-t01); FORGED part: Air-Way NON-forged row FF2501-8-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on JJ FLATS=0.875 vs Air-Way S2=0.94 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5369 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p8 FS2501-08-08-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
+          <t>forged (-FG): Air-Way non-forged FF2501-8-6-O = Brennan forged FS2501-08-06-FG p8 on every compared cell (M LGTH ~ L7, N LGTH ~ N, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5368 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>FS2501-08-08-FG</t>
+          <t>FS2501-08-06-FG</t>
         </is>
       </c>
     </row>
@@ -1354,14 +1354,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FS2501-08-06-FG</t>
+          <t>FS2501-08-08-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="D6" t="n">
         <v>0.40625</v>
@@ -1385,22 +1385,22 @@
         <v>0.2125</v>
       </c>
       <c r="K6" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="L6" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="M6" t="n">
-        <v>0.32823</v>
+        <v>0.40779</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4078</v>
+        <v>0.5337</v>
       </c>
       <c r="O6" t="n">
         <v>1.7899</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1522</v>
+        <v>0.2163</v>
       </c>
       <c r="Q6" t="n">
         <v>0.37</v>
@@ -1409,10 +1409,10 @@
         <v>1.1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="T6" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="U6" t="n">
         <v>0.8125</v>
@@ -1433,58 +1433,58 @@
         <v>0.0625</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.65645</v>
+        <v>0.81557</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.4078</v>
+        <v>0.5337</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.05556</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.32823</v>
+        <v>0.40779</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.28378</v>
+        <v>0.35064</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="AH6" t="n">
         <v>0.596</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.21601</v>
+        <v>0.25209</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.21601</v>
+        <v>0.25209</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.43251</v>
+        <v>0.50468</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>FS2501-08-06-FG</t>
+          <t>FS2501-08-08-FG</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 13/16-16 UN (male O-ring face seal, SAE J1453) x 3/8-18 NPTF</t>
+          <t>ORFS 90 deg Male Elbow (male face seal x male pipe), 13/16-16 UN (male O-ring face seal, SAE J1453) x 1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>Air-Way FF2501 (s21, double-pass 2026-10-15, parts.air-way.com/api/series/21, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2501-08-06-FG (ORFS-p008-t01); FORGED part: Air-Way NON-forged row FF2501-8-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "M LGTH" = "1.10" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 118.0, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; N@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "N LGTH" = "1.47" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 118.0, page verified True) [Brennan = yes 2026-10-18] - pipe leg tip -&gt; crossing; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "JJ FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 118.0, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 7/7 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -08 = 0.8125 (PLAN.md s2 FS_THR / the -08 thread of every staged ORFS row); = Brennan "A THREAD" "13/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "A THREAD" "13/16-16" in the table's format; $PRP@Thread_A: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "B THREAD" "1/2-14" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p8 table ORFS-p008-t01 "FS2501-FG MFS-MP 90 DEG ELBOW" row FS2501-08-08-FG col "TUBE O.D." "1/2" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2501: FSM -08 bore on 2 Air-Way row(s): 0.37 (unanimous) [Air-Way, not Brennan]; D2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2501: NPTF -08 bore on 1 Air-Way row(s): 0.53 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged FF2501-8-6-O = Brennan forged FS2501-08-06-FG p8 on every compared cell (M LGTH ~ L7, N LGTH ~ N, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5368 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on JJ FLATS=0.875 vs Air-Way S2=0.94 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF2501 is used only where Brennan FS2501-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5369 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p8 FS2501-08-08-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>FS2501-08-06-FG</t>
+          <t>FS2501-08-08-FG</t>
         </is>
       </c>
     </row>
